--- a/standard-word-analysis/sample/standard-word-table.v1.sample.xlsx
+++ b/standard-word-analysis/sample/standard-word-table.v1.sample.xlsx
@@ -7,31 +7,23 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="keywords" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="keywords" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'keywords'!$A$1:$J$4</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.000000"/>
-  </numFmts>
-  <fonts count="2">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -54,12 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,227 +413,114 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>standardWordTableVersion</t>
+          <t>keyword</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>v1</t>
+          <t>对应域名</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>sourcePresence(SIM/SEM)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>score(simWindowVolume*cpc/kd)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>volume(sim)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>kd(sim)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>cpc(sim)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>volume(sem)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>kd(sem)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>cpc(sem)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>gefeiKD</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>scoreFormula</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>simWindowVolume * simCpc / simKd</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>rowCount</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>3</v>
+          <t>image to text</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>image to text | image-to-text</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>both（SIM+SEM）</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>96</v>
+      </c>
+      <c r="F2" t="n">
+        <v>12000</v>
+      </c>
+      <c r="G2" t="n">
+        <v>50</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I2" t="n">
+        <v>18100</v>
+      </c>
+      <c r="J2" t="n">
+        <v>68</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="L2" t="n">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>keyword</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>group</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>sourcePresence(SIM/SEM)</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>score(simWindowVolume*cpc/kd)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>volume(sim)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>kd(sim)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>cpc(sim)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>volume(sem)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>kd(sem)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>cpc(sem)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>image to text</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>image to text | image-to-text</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>both（SIM+SEM）</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>96</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>12000</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="G2" s="4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>18100</v>
-      </c>
-      <c r="I2" s="4" t="n">
-        <v>68</v>
-      </c>
-      <c r="J2" s="4" t="n">
-        <v>1.88</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>free image parser</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>free image parser | free images parser</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>sim_only（仅 SIM）</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>12.766667</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>2300</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="G3" s="4" t="n">
-        <v>0.166522</v>
-      </c>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="4" t="n"/>
-      <c r="J3" s="4" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ocr screenshot online</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ocr screenshot online</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>sem_only（仅 SEM）</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" s="4" t="n"/>
-      <c r="G4" s="4" t="n"/>
-      <c r="H4" s="3" t="n">
-        <v>540</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>47</v>
-      </c>
-      <c r="J4" s="4" t="n">
-        <v>0.62</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:J4"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>